--- a/driver_forms/005_van_safety_checklist--driver_forms.xlsx
+++ b/driver_forms/005_van_safety_checklist--driver_forms.xlsx
@@ -1,15 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -32,7 +31,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -43,12 +42,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
         <bgColor rgb="004472C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0070AD47"/>
-        <bgColor rgb="0070AD47"/>
       </patternFill>
     </fill>
   </fills>
@@ -64,12 +57,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -440,9 +430,9 @@
   <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +515,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Van Safety Checklist 1</t>
+          <t>Is the van's tires in good condition?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +538,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Van Safety Checklist 2</t>
+          <t>Are the van's brakes functioning properly?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +561,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Van Safety Check</t>
+          <t>Is the van's fuel level adequate?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +584,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Van Safety Check 2</t>
+          <t>Are the van's lights and reflectors in good working order?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +607,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Van Safety Check List 1</t>
+          <t>Is the van's horn functioning properly?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +630,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Van Safety Check List 1</t>
+          <t>Are the van's mirrors adjusted properly?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,7 +643,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -663,7 +653,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Van Safety Checklist</t>
+          <t>Is the van's cargo secure?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,7 +666,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -686,7 +676,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Van Safety Checklist 2</t>
+          <t>Are the van's doors locked and secure?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,7 +689,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -709,7 +699,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Van Safety Check 1</t>
+          <t>Is the van's fire extinguisher working properly?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +722,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Van Safety Check 2</t>
+          <t>Are the van's first aid kit and emergency equipment in good condition?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -755,7 +745,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Van Safety Check 3</t>
+          <t>Are the van's tires properly inflated?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,7 +768,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Van Safety Check 4</t>
+          <t>Are the van's brakes functioning properly during an emergency stop?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -801,7 +791,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Van Safety Check 5</t>
+          <t>Is the van's steering and suspension in good condition?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +814,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Van Safety Check 6</t>
+          <t>Are the van's seats and seatbelts in good condition?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +837,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Van Safety Check 7</t>
+          <t>Are the van's seatbelts properly fastened?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,7 +860,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Van Safety Check 8</t>
+          <t>Is the van's fuel level adequate for the trip?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +883,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Van Safety Check 9</t>
+          <t>Are the van's lights and reflectors functioning properly during an emergency stop?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +901,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>van_safety_checklist_form_18</t>
+          <t>van_safety_checklist_form_17_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Van Safety Check 10</t>
+          <t>Is the van's emergency kit and equipment up to date?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +924,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>van_safety_checklist_form_19</t>
+          <t>van_safety_checklist_form_18</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Van Safety Check 11</t>
+          <t>Are the van's seats and seatbelts inspected regularly?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +947,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>van_safety_checklist_form_20</t>
+          <t>van_safety_checklist_form_19</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Van Safety Check 12</t>
+          <t>Are the van's steering and suspension inspected regularly?</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +970,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>van_safety_checklist_form_21</t>
+          <t>van_safety_checklist_form_20</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Van Safety Check 13</t>
+          <t>Are the van's tires properly rotated?</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +993,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>van_safety_checklist_form_22</t>
+          <t>van_safety_checklist_form_21</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Van Safety Check 14</t>
+          <t>Are the van's brakes inspected and maintained regularly?</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1016,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>van_safety_checklist_form_23</t>
+          <t>van_safety_checklist_form_22</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Van Safety Check 15</t>
+          <t>Are the van's seatbelts functioning properly?</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1039,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>van_safety_checklist_form_24</t>
+          <t>van_safety_checklist_form_23</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Van Safety Check 16</t>
+          <t>Is the van's first aid kit and emergency equipment inspected regularly?</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1077,7 +1067,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Van Safety Check 17</t>
+          <t>Are the van's mirrors adjusted and inspected regularly?</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1093,144 +1083,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>list_name</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>label</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>van_safety_checklist_form_7_choices</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>van_safety_checklist_form_7_choices</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>van_safety_checklist_form_8_choices</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>van_safety_checklist_form_8_choices</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>van_safety_checklist_form_9_choices</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>van_safety_checklist_form_9_choices</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
